--- a/backend/data/dc_inventory.xlsx
+++ b/backend/data/dc_inventory.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rack-01" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Rack-02" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Rack-03" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Rack-04" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Rack-05" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Rack-06" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Rack-07" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Rack-08" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Rack-09" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Rack-10" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Rack-11" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Rack-12" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Rack-13" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Rack-15" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Rack-17" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Rack-18" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-01" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-02" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-03" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-04" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-05" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-06" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-07" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-08" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-09" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-10" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-11" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-12" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-13" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-15" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-17" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rack-18" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1311,6 +1311,61 @@
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-17</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FOC2116U0G1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>WS-C3850-48T-E</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vlan1212</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>172.17.12.17</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>IOS-XE</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Lalit/Gopala</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
